--- a/data/credit_bond_2026-07-28.xlsx
+++ b/data/credit_bond_2026-07-28.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-07-29" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-07-30" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-29</t>
+          <t>数据来源：DM    2026-07-30</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,9 @@
       <c r="H3" s="4" t="n">
         <v>1.59</v>
       </c>
-      <c r="I3" s="3"/>
+      <c r="I3" s="4" t="n">
+        <v>30.59</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.61</t>
@@ -737,7 +739,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.5900/--</t>
+          <t>1.5950/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">

--- a/data/credit_bond_2026-07-28.xlsx
+++ b/data/credit_bond_2026-07-28.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-07-30" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-07-31" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-30</t>
+          <t>数据来源：DM    2026-07-31</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="V3" s="3"/>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
           <t>1.63%~1.73%</t>

--- a/data/credit_bond_2026-07-28.xlsx
+++ b/data/credit_bond_2026-07-28.xlsx
@@ -838,7 +838,7 @@
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AL3" s="3" t="inlineStr">

--- a/data/credit_bond_2026-07-28.xlsx
+++ b/data/credit_bond_2026-07-28.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-07-31" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-03" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -173,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-31</t>
+          <t>数据来源：DM    2026-08-03</t>
         </is>
       </c>
     </row>
@@ -907,6 +907,235 @@
         </is>
       </c>
       <c r="AY3" s="3"/>
+    </row>
+    <row r="4" customHeight="true" ht="18.0">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>26农业银行绿色债01</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>08-03 18:00</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2628001.IB</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1.20 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>25农业银行绿色债02</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>3.57Y</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>1.5338</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>中国农业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>08-03 09:00</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>1.52%~1.62%</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于《绿色金融支持项目目录（2025年版）》规定的绿色产业项目。</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,华泰证券股份有限公司,招商证券股份有限公司,中银国际证券股份有限公司,国投证券股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>中央国有企业</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>中国农业银行股份有限公司2026年绿色金融债券(第一期)(债券通)</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>2029-08-05</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>国有银行</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AY4" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-07-28.xlsx
+++ b/data/credit_bond_2026-07-28.xlsx
@@ -964,7 +964,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4700</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
